--- a/docs/ValueSet-ahip-sexual-orientation.xlsx
+++ b/docs/ValueSet-ahip-sexual-orientation.xlsx
@@ -50,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,7 +86,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Based on SNOMED CT and US Core Orientation Value Set</t>
+    <t>Used as the answer options for the sexual orientation question in the SOGI and Relationship Status Section, capturing how a patient currently thinks of their sexual orientation. Based on SNOMED CT and US Core Orientation Value Set</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -155,7 +155,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
   <si>
     <t>ASKU</t>

--- a/docs/ValueSet-ahip-sexual-orientation.xlsx
+++ b/docs/ValueSet-ahip-sexual-orientation.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -143,10 +143,13 @@
     <t>http://snomed.info/sct</t>
   </si>
   <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
+    <t>ASKU</t>
+  </si>
+  <si>
+    <t>I don't know</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
   <si>
     <t>CNTR</t>
@@ -156,15 +159,6 @@
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
-  </si>
-  <si>
-    <t>ASKU</t>
-  </si>
-  <si>
-    <t>I don't know</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -508,7 +502,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -533,26 +527,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -579,10 +565,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -598,7 +584,7 @@
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-sexual-orientation.xlsx
+++ b/docs/ValueSet-ahip-sexual-orientation.xlsx
@@ -95,7 +95,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement.
+This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -110,19 +112,19 @@
     <t>20430005</t>
   </si>
   <si>
-    <t>Straight or heterosexual (attracted to gender different from your own)​</t>
+    <t>Straight or heterosexual (attracted to gender different from your own)</t>
   </si>
   <si>
     <t>38628009</t>
   </si>
   <si>
-    <t>Gay or lesbian (attracted to the same gender as your own)​</t>
+    <t>Gay or lesbian (attracted to the same gender as your own)</t>
   </si>
   <si>
     <t>42035005</t>
   </si>
   <si>
-    <t>Bisexual (attracted to same gender as your own and gender different from your own)​</t>
+    <t>Bisexual (attracted to same gender as your own and gender different from your own)</t>
   </si>
   <si>
     <t>765288000</t>
@@ -134,7 +136,7 @@
     <t>51431000087101</t>
   </si>
   <si>
-    <t>Pansexual (attracted to any gender)​</t>
+    <t>Pansexual (attracted to any gender)</t>
   </si>
   <si>
     <t>System URI</t>
@@ -158,7 +160,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
